--- a/public/mis/data/description.xlsx
+++ b/public/mis/data/description.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangxuewen02/app/workspace/family/zdss/webserver-zdss-mapi/public/mis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77F1343-FB74-CC4B-B5E3-640D02BE356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6F168D-3916-B146-89E2-80E3FF02E2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1840" yWindow="4280" windowWidth="28240" windowHeight="17400" xr2:uid="{7D35C25F-08F6-3F49-AAC2-1114344C77DF}"/>
+    <workbookView xWindow="1840" yWindow="820" windowWidth="28240" windowHeight="17400" xr2:uid="{7D35C25F-08F6-3F49-AAC2-1114344C77DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>前置材料</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,10 +54,6 @@
   </si>
   <si>
     <t>正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>音频地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -313,6 +309,18 @@
     <t/>
   </si>
   <si>
+    <t>材料类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACCC1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://example.com/audio6.mp3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>说明:
 考题分</t>
@@ -347,7 +355,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>题目组类似&lt;阅读理解&gt;和&lt;完形填空&gt;</t>
+      <t>题目组类似&lt;阅读理解&gt;&lt;完形填空&gt;&lt;听力&gt;</t>
     </r>
     <r>
       <rPr>
@@ -402,7 +410,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">题目组必填(只填第一个即可)  </t>
+      <t>题目组必填(只填第一个即可)  ,  阅读题填内容,   听力题填有效音频地址</t>
     </r>
     <r>
       <rPr>
@@ -424,14 +432,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">- 题型:   必填, 1选择, 2多选, 3判断, 4,填空,  5,简答, 6写作,  7听力, 8口语   
+      <t xml:space="preserve">- 题型:   必填, 1选择, 2多选, 3判断, 4,填空,  5,简答, 6写作,  7口语   
 - 难度:   非必填  默认2,    1:非常简单,  2:简单,  3:一般,  4:较难,  5: 困难
 - 分值:   非必填  默认5     输入值为: 1-99 
 - 标签id : 非必填,  通过平台查看标签id,  一题最多写3个,  用英文逗号分隔,
 - 科目id:  非必填,  通过平台查看科目id,  一题最多写1个
-- 音频地址: 配置音频地址即可
 - 题干:  必填  长度500字符以内 (填空题需要用5个_ 作为填写项)
-- 答案:  一行一个答案,   选择/多选/填空/判断题  最少2个,  最多6个,   简答题/写作题/听力题/口语题不写,  </t>
+- 答案:  一行一个答案,   选择/多选/填空/判断题  最少2个,  最多6个,   简答题/写作题/口语题不写,  </t>
     </r>
     <r>
       <rPr>
@@ -486,7 +493,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -554,6 +561,15 @@
       <family val="4"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -593,17 +609,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -623,15 +639,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -947,214 +967,220 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="2" width="26.1640625" customWidth="1"/>
-    <col min="3" max="3" width="45.5" customWidth="1"/>
-    <col min="4" max="4" width="6.1640625" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" customWidth="1"/>
-    <col min="8" max="8" width="11.1640625" customWidth="1"/>
-    <col min="9" max="9" width="36.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" customWidth="1"/>
     <col min="10" max="10" width="44.5" customWidth="1"/>
     <col min="11" max="11" width="22.5" customWidth="1"/>
     <col min="12" max="12" width="10.5" customWidth="1"/>
     <col min="13" max="13" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1" ht="74" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:13" s="5" customFormat="1" ht="74" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="128" customHeight="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13" ht="187">
+      <c r="A3" s="3">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="3">
+        <v>2</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="85">
+      <c r="A4" s="3">
+        <v>1001</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
         <v>3</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="6" t="s">
+      <c r="G4" s="3">
         <v>4</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="128" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" ht="129" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="4">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" ht="120" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3">
         <v>2</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2"/>
-      <c r="J2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" ht="221">
-      <c r="A3" s="4">
-        <v>1001</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="4">
-        <v>2</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="170">
-      <c r="A4" s="4">
-        <v>1001</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4">
-        <v>3</v>
-      </c>
-      <c r="F4" s="4">
-        <v>4</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" ht="129" customHeight="1">
-      <c r="A5" s="4">
-        <v>1001</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4">
-        <v>4</v>
-      </c>
-      <c r="F5" s="4">
-        <v>2</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="4">
-        <v>1</v>
-      </c>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" ht="120" customHeight="1">
-      <c r="A6" s="4">
-        <v>1001</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4">
-        <v>4</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
     </row>
     <row r="9" spans="1:13" ht="16" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -1162,7 +1188,8 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="8"/>
@@ -1172,7 +1199,8 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="8"/>
@@ -1182,7 +1210,8 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="8"/>
@@ -1192,7 +1221,8 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="8"/>
@@ -1202,7 +1232,8 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="8"/>
@@ -1212,7 +1243,8 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="8"/>
@@ -1222,7 +1254,8 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="8"/>
@@ -1232,9 +1265,10 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="H16" s="8"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1242,9 +1276,10 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="H17" s="8"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -1252,8 +1287,9 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -1261,8 +1297,9 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -1270,8 +1307,9 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -1279,8 +1317,9 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1288,8 +1327,9 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -1297,8 +1337,9 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -1306,8 +1347,9 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -1315,8 +1357,9 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -1324,8 +1367,9 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -1333,8 +1377,9 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -1342,8 +1387,9 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -1351,17 +1397,21 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="9" t="s">
-        <v>29</v>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:G29"/>
+    <mergeCell ref="A9:H29"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{C2EC3E79-B682-CE4B-A705-A7D7B5E1307A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/mis/data/description.xlsx
+++ b/public/mis/data/description.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangxuewen02/app/workspace/family/zdss/webserver-zdss-mapi/public/mis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6F168D-3916-B146-89E2-80E3FF02E2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D9F61D-90DD-5E48-8CEA-5B17CB4B81AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1840" yWindow="820" windowWidth="28240" windowHeight="17400" xr2:uid="{7D35C25F-08F6-3F49-AAC2-1114344C77DF}"/>
+    <workbookView xWindow="1840" yWindow="760" windowWidth="28240" windowHeight="17380" xr2:uid="{7D35C25F-08F6-3F49-AAC2-1114344C77DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,13 +35,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>前置材料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>科目id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -318,6 +314,14 @@
   </si>
   <si>
     <t>https://example.com/audio6.mp3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来源id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -436,7 +440,7 @@
 - 难度:   非必填  默认2,    1:非常简单,  2:简单,  3:一般,  4:较难,  5: 困难
 - 分值:   非必填  默认5     输入值为: 1-99 
 - 标签id : 非必填,  通过平台查看标签id,  一题最多写3个,  用英文逗号分隔,
-- 科目id:  非必填,  通过平台查看科目id,  一题最多写1个
+- 来源id : 非必填,  通过平台查看来源id,  一题最多写3个,  用英文逗号分隔,
 - 题干:  必填  长度500字符以内 (填空题需要用5个_ 作为填写项)
 - 答案:  一行一个答案,   选择/多选/填空/判断题  最少2个,  最多6个,   简答题/写作题/口语题不写,  </t>
     </r>
@@ -622,9 +626,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -642,11 +643,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -972,436 +976,449 @@
     <col min="5" max="5" width="6.1640625" customWidth="1"/>
     <col min="6" max="6" width="7.33203125" customWidth="1"/>
     <col min="7" max="7" width="6.33203125" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.1640625" customWidth="1"/>
+    <col min="8" max="9" width="11.33203125" customWidth="1"/>
     <col min="10" max="10" width="44.5" customWidth="1"/>
     <col min="11" max="11" width="22.5" customWidth="1"/>
     <col min="12" max="12" width="10.5" customWidth="1"/>
     <col min="13" max="13" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" ht="74" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:13" s="4" customFormat="1" ht="74" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="128" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" ht="187">
+      <c r="A3" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="2">
+        <v>2</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="85">
+      <c r="A4" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" ht="129" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="5" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="2">
         <v>1</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="5" t="s">
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" ht="120" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2">
         <v>4</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="128" customHeight="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="G6" s="2">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" ht="187">
-      <c r="A3" s="3">
-        <v>1001</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>3</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="3">
-        <v>2</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="85">
-      <c r="A4" s="3">
-        <v>1001</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" ht="129" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>3</v>
-      </c>
-      <c r="F5" s="3">
-        <v>4</v>
-      </c>
-      <c r="G5" s="3">
-        <v>2</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="3">
-        <v>1</v>
-      </c>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="120" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3">
-        <v>4</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3">
-        <v>2</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="2" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="9" spans="1:13" ht="16" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="9" spans="1:13" ht="16" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
